--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -21239,12 +21239,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21278,81 +21278,100 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>15153</v>
+        <v>2584</v>
       </c>
       <c r="O123" t="n">
-        <v>15153</v>
+        <v>2584</v>
       </c>
       <c r="R123" t="n">
-        <v>4.341392282585449</v>
+        <v>24.14717102668417</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21379,17 +21398,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21414,7 +21433,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21423,81 +21442,175 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>14684</v>
+        <v>2584</v>
       </c>
       <c r="O124" t="n">
-        <v>14684</v>
-      </c>
-      <c r="R124" t="n">
-        <v>4.207021994158565</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2584</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21559,7 +21672,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -21568,13 +21681,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>14554</v>
+        <v>15153</v>
       </c>
       <c r="O125" t="n">
-        <v>14554</v>
+        <v>15153</v>
       </c>
       <c r="R125" t="n">
-        <v>4.169776498432563</v>
+        <v>4.341392282585449</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21704,7 +21817,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21713,13 +21826,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>13669</v>
+        <v>14684</v>
       </c>
       <c r="O126" t="n">
-        <v>13669</v>
+        <v>14684</v>
       </c>
       <c r="R126" t="n">
-        <v>3.916220623682472</v>
+        <v>4.207021994158565</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -21849,7 +21962,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21858,13 +21971,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>16595</v>
+        <v>14554</v>
       </c>
       <c r="O127" t="n">
-        <v>16595</v>
+        <v>14554</v>
       </c>
       <c r="R127" t="n">
-        <v>4.754530781330795</v>
+        <v>4.169776498432563</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21964,12 +22077,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21994,22 +22107,22 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>376</v>
+        <v>13669</v>
       </c>
       <c r="O128" t="n">
-        <v>376</v>
+        <v>13669</v>
       </c>
       <c r="R128" t="n">
-        <v>1.380977244139441</v>
+        <v>3.916220623682472</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22042,42 +22155,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22109,12 +22222,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22139,109 +22252,90 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>41</v>
+        <v>16595</v>
       </c>
       <c r="O129" t="n">
-        <v>41</v>
+        <v>16595</v>
       </c>
       <c r="R129" t="n">
-        <v>0.7293117600542963</v>
+        <v>4.754530781330795</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22268,217 +22362,526 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>376</v>
+      </c>
+      <c r="O130" t="n">
+        <v>376</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1.380977244139441</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>80</v>
+      </c>
+      <c r="O131" t="n">
+        <v>80</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1.42304733669131</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>D094</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Chlamydia trachomatis infection</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
         <is>
           <t>沙眼衣原体感染</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N130" t="n">
-        <v>41</v>
-      </c>
-      <c r="O130" t="n">
-        <v>41</v>
-      </c>
-      <c r="U130" t="inlineStr">
+      <c r="N132" t="n">
+        <v>80</v>
+      </c>
+      <c r="O132" t="n">
+        <v>80</v>
+      </c>
+      <c r="U132" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
+      <c r="V132" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
+      <c r="W132" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>Chlamydia</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Y132" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA130" t="inlineStr">
+      <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
+      <c r="AB132" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
+      <c r="AC132" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD130" t="inlineStr">
+      <c r="AD132" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE130" t="inlineStr">
+      <c r="AE132" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF130" t="inlineStr">
+      <c r="AF132" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG130" t="inlineStr">
+      <c r="AG132" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH130" t="inlineStr">
+      <c r="AH132" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI130" t="inlineStr">
+      <c r="AI132" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ130" t="inlineStr">
+      <c r="AJ132" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK130" t="inlineStr">
+      <c r="AK132" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
+      <c r="AM132" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN130" t="b">
+      <c r="AN132" t="b">
         <v>1</v>
       </c>
-      <c r="AO130" t="inlineStr">
+      <c r="AO132" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP130" t="inlineStr">
+      <c r="AP132" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ130" t="inlineStr">
+      <c r="AQ132" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR130" t="inlineStr">
+      <c r="AR132" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS130" t="inlineStr">
+      <c r="AS132" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="AT130" t="n">
+      <c r="AT132" t="n">
         <v>2</v>
       </c>
-      <c r="AU130" t="inlineStr">
+      <c r="AU132" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV130" t="inlineStr">
+      <c r="AV132" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW130" t="inlineStr">
+      <c r="AW132" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
+      <c r="AX132" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY130" t="inlineStr">
+      <c r="AY132" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
+      <c r="AZ132" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA130" t="inlineStr">
+      <c r="BA132" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB130" t="inlineStr">
+      <c r="BB132" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC130" t="inlineStr">
+      <c r="BC132" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -22600,7 +23003,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -22610,7 +23013,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -22630,7 +23033,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -22662,7 +23065,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>551495</v>
+        <v>554118</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8110</v>
+        <v>8113</v>
       </c>
       <c r="O95" t="n">
-        <v>8110</v>
+        <v>8113</v>
       </c>
       <c r="R95" t="n">
-        <v>29.7865038563055</v>
+        <v>29.79752229176406</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19594,13 +19594,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7290</v>
+        <v>7332</v>
       </c>
       <c r="O112" t="n">
-        <v>7290</v>
+        <v>7332</v>
       </c>
       <c r="R112" t="n">
-        <v>26.77479816429927</v>
+        <v>26.9290562607191</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="O121" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="R121" t="n">
-        <v>19.42459614583638</v>
+        <v>19.46017232925367</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="O122" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -22551,13 +22551,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="O131" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="R131" t="n">
-        <v>1.42304733669131</v>
+        <v>1.956690087950551</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22715,10 +22715,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="O132" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>554118</v>
+        <v>554195</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8113</v>
+        <v>8114</v>
       </c>
       <c r="O95" t="n">
-        <v>8113</v>
+        <v>8114</v>
       </c>
       <c r="R95" t="n">
-        <v>29.79752229176406</v>
+        <v>29.80119510358358</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19594,13 +19594,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7332</v>
+        <v>7366</v>
       </c>
       <c r="O112" t="n">
-        <v>7332</v>
+        <v>7366</v>
       </c>
       <c r="R112" t="n">
-        <v>26.9290562607191</v>
+        <v>27.05393186258278</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="O121" t="n">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="R121" t="n">
-        <v>19.46017232925367</v>
+        <v>19.63805324634008</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="O122" t="n">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -22551,13 +22551,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="O131" t="n">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="R131" t="n">
-        <v>1.956690087950551</v>
+        <v>3.433101699767786</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22715,10 +22715,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="O132" t="n">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>554195</v>
+        <v>554323</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -19594,13 +19594,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7366</v>
+        <v>7398</v>
       </c>
       <c r="O112" t="n">
-        <v>7366</v>
+        <v>7398</v>
       </c>
       <c r="R112" t="n">
-        <v>27.05393186258278</v>
+        <v>27.17146184080741</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O121" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="R121" t="n">
-        <v>19.63805324634008</v>
+        <v>19.65584133804872</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O122" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -22551,13 +22551,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="O131" t="n">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="R131" t="n">
-        <v>3.433101699767786</v>
+        <v>4.358082468617137</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22715,10 +22715,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="O132" t="n">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -22884,6 +22884,151 @@
       <c r="BC132" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>14539</v>
+      </c>
+      <c r="O133" t="n">
+        <v>14539</v>
+      </c>
+      <c r="R133" t="n">
+        <v>4.16547894123341</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22920,7 +23065,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23148,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -23013,7 +23158,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -23065,7 +23210,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>554323</v>
+        <v>568947</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="O3" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="O4" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="O18" t="n">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="O19" t="n">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3158</v>
+        <v>3160</v>
       </c>
       <c r="O32" t="n">
-        <v>3158</v>
+        <v>3160</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3158</v>
+        <v>3160</v>
       </c>
       <c r="O33" t="n">
-        <v>3158</v>
+        <v>3160</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="O46" t="n">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="O47" t="n">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="O60" t="n">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="O61" t="n">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>3092</v>
+        <v>3104</v>
       </c>
       <c r="O83" t="n">
-        <v>3092</v>
+        <v>3104</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -14904,10 +14904,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>3092</v>
+        <v>3104</v>
       </c>
       <c r="O84" t="n">
-        <v>3092</v>
+        <v>3104</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -18169,12 +18169,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18208,22 +18208,19 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1033</v>
+        <v>3227</v>
       </c>
       <c r="O104" t="n">
-        <v>1033</v>
-      </c>
-      <c r="R104" t="n">
-        <v>18.37509873502654</v>
+        <v>3227</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -18238,70 +18235,65 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18333,12 +18325,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18372,29 +18364,29 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1033</v>
+        <v>3227</v>
       </c>
       <c r="O105" t="n">
-        <v>1033</v>
+        <v>3227</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Chlamydia</t>
+          <t>Chlamydial Infections</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -18404,7 +18396,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -18419,7 +18411,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -18454,17 +18446,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -18477,70 +18469,65 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18572,12 +18559,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18611,13 +18598,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2289</v>
+        <v>1033</v>
       </c>
       <c r="O106" t="n">
-        <v>2289</v>
+        <v>1033</v>
       </c>
       <c r="R106" t="n">
-        <v>21.39043130034058</v>
+        <v>18.37509873502654</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -18626,7 +18613,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -18646,7 +18633,7 @@
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -18656,7 +18643,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -18664,47 +18651,47 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18736,12 +18723,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18775,29 +18762,29 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2289</v>
+        <v>1033</v>
       </c>
       <c r="O107" t="n">
-        <v>2289</v>
+        <v>1033</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Chlamydia</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -18822,7 +18809,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -18857,17 +18844,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -18885,7 +18872,7 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -18895,7 +18882,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -18903,47 +18890,47 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18975,12 +18962,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19005,7 +18992,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19014,81 +19001,100 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>10203</v>
+        <v>2289</v>
       </c>
       <c r="O108" t="n">
-        <v>10203</v>
+        <v>2289</v>
       </c>
       <c r="R108" t="n">
-        <v>2.923198406864604</v>
+        <v>21.39043130034058</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19115,17 +19121,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19150,7 +19156,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19159,81 +19165,175 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>13432</v>
+        <v>2289</v>
       </c>
       <c r="O109" t="n">
-        <v>13432</v>
-      </c>
-      <c r="R109" t="n">
-        <v>3.848319219935838</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2289</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19395,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19304,13 +19404,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="O110" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="R110" t="n">
-        <v>3.852330273321715</v>
+        <v>2.923198406864604</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19440,7 +19540,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19449,13 +19549,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="O111" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="R111" t="n">
-        <v>4.024232561287879</v>
+        <v>3.848319219935838</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -19555,12 +19655,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19585,22 +19685,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7398</v>
+        <v>13446</v>
       </c>
       <c r="O112" t="n">
-        <v>7398</v>
+        <v>13446</v>
       </c>
       <c r="R112" t="n">
-        <v>27.17146184080741</v>
+        <v>3.852330273321715</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -19633,42 +19733,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19700,12 +19800,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19730,23 +19830,26 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>73</v>
+        <v>14046</v>
       </c>
       <c r="O113" t="n">
-        <v>73</v>
+        <v>14046</v>
+      </c>
+      <c r="R113" t="n">
+        <v>4.024232561287879</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -19775,42 +19878,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19842,12 +19945,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19881,14 +19984,17 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1939</v>
+        <v>7398</v>
       </c>
       <c r="O114" t="n">
-        <v>1939</v>
+        <v>7398</v>
+      </c>
+      <c r="R114" t="n">
+        <v>27.17146184080741</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -19922,12 +20028,12 @@
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -19942,12 +20048,12 @@
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
@@ -19984,12 +20090,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20023,10 +20129,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="O115" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20064,7 +20170,7 @@
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
@@ -20084,7 +20190,7 @@
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
@@ -20126,12 +20232,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20165,10 +20271,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1738</v>
+        <v>1939</v>
       </c>
       <c r="O116" t="n">
-        <v>1738</v>
+        <v>1939</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -20206,7 +20312,7 @@
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
@@ -20226,7 +20332,7 @@
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
@@ -20268,12 +20374,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20307,10 +20413,10 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>345</v>
+        <v>51</v>
       </c>
       <c r="O117" t="n">
-        <v>345</v>
+        <v>51</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20348,7 +20454,7 @@
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
@@ -20368,7 +20474,7 @@
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
@@ -20410,12 +20516,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20449,10 +20555,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>93</v>
+        <v>1738</v>
       </c>
       <c r="O118" t="n">
-        <v>93</v>
+        <v>1738</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20490,7 +20596,7 @@
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
@@ -20510,7 +20616,7 @@
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
@@ -20552,12 +20658,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20591,10 +20697,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1335</v>
+        <v>345</v>
       </c>
       <c r="O119" t="n">
-        <v>1335</v>
+        <v>345</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20632,7 +20738,7 @@
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
@@ -20652,7 +20758,7 @@
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
@@ -20694,12 +20800,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20733,10 +20839,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>851</v>
+        <v>93</v>
       </c>
       <c r="O120" t="n">
-        <v>851</v>
+        <v>93</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20774,7 +20880,7 @@
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
@@ -20794,7 +20900,7 @@
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
@@ -20836,12 +20942,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20875,100 +20981,78 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1105</v>
+        <v>1335</v>
       </c>
       <c r="O121" t="n">
-        <v>1105</v>
-      </c>
-      <c r="R121" t="n">
-        <v>19.65584133804872</v>
+        <v>1335</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20995,17 +21079,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21039,175 +21123,78 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1105</v>
+        <v>851</v>
       </c>
       <c r="O122" t="n">
-        <v>1105</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
+        <v>851</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT122" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV122" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21239,12 +21226,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21278,13 +21265,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2584</v>
+        <v>1105</v>
       </c>
       <c r="O123" t="n">
-        <v>2584</v>
+        <v>1105</v>
       </c>
       <c r="R123" t="n">
-        <v>24.14717102668417</v>
+        <v>19.65584133804872</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21293,7 +21280,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21313,7 +21300,7 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
@@ -21323,7 +21310,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21331,47 +21318,47 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21403,12 +21390,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21442,29 +21429,29 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2584</v>
+        <v>1105</v>
       </c>
       <c r="O124" t="n">
-        <v>2584</v>
+        <v>1105</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Chlamydia</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -21489,7 +21476,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -21524,17 +21511,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -21552,7 +21539,7 @@
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
@@ -21562,7 +21549,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21570,47 +21557,47 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21642,12 +21629,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21681,81 +21668,100 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>15153</v>
+        <v>2584</v>
       </c>
       <c r="O125" t="n">
-        <v>15153</v>
+        <v>2584</v>
       </c>
       <c r="R125" t="n">
-        <v>4.341392282585449</v>
+        <v>24.14717102668417</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21782,17 +21788,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21817,7 +21823,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21826,81 +21832,175 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>14684</v>
+        <v>2584</v>
       </c>
       <c r="O126" t="n">
-        <v>14684</v>
-      </c>
-      <c r="R126" t="n">
-        <v>4.207021994158565</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2584</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21962,7 +22062,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21971,13 +22071,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>14554</v>
+        <v>15153</v>
       </c>
       <c r="O127" t="n">
-        <v>14554</v>
+        <v>15153</v>
       </c>
       <c r="R127" t="n">
-        <v>4.169776498432563</v>
+        <v>4.341392282585449</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22107,7 +22207,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22116,13 +22216,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>13669</v>
+        <v>14684</v>
       </c>
       <c r="O128" t="n">
-        <v>13669</v>
+        <v>14684</v>
       </c>
       <c r="R128" t="n">
-        <v>3.916220623682472</v>
+        <v>4.207021994158565</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22252,7 +22352,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22261,13 +22361,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>16595</v>
+        <v>14554</v>
       </c>
       <c r="O129" t="n">
-        <v>16595</v>
+        <v>14554</v>
       </c>
       <c r="R129" t="n">
-        <v>4.754530781330795</v>
+        <v>4.169776498432563</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22367,12 +22467,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22397,22 +22497,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>376</v>
+        <v>13669</v>
       </c>
       <c r="O130" t="n">
-        <v>376</v>
+        <v>13669</v>
       </c>
       <c r="R130" t="n">
-        <v>1.380977244139441</v>
+        <v>3.916220623682472</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22445,42 +22545,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22512,12 +22612,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22542,109 +22642,90 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>245</v>
+        <v>16595</v>
       </c>
       <c r="O131" t="n">
-        <v>245</v>
+        <v>16595</v>
       </c>
       <c r="R131" t="n">
-        <v>4.358082468617137</v>
+        <v>4.754530781330795</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22671,17 +22752,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22715,175 +22796,81 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>245</v>
+        <v>376</v>
       </c>
       <c r="O132" t="n">
-        <v>245</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
+        <v>376</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1.380977244139441</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT132" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22915,118 +22902,521 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>245</v>
+      </c>
+      <c r="O133" t="n">
+        <v>245</v>
+      </c>
+      <c r="R133" t="n">
+        <v>4.358082468617137</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>245</v>
+      </c>
+      <c r="O134" t="n">
+        <v>245</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>D094</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Chlamydia trachomatis infection</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>沙眼衣原体感染</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N133" t="n">
+      <c r="N135" t="n">
         <v>14539</v>
       </c>
-      <c r="O133" t="n">
+      <c r="O135" t="n">
         <v>14539</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R135" t="n">
         <v>4.16547894123341</v>
       </c>
-      <c r="S133" t="inlineStr">
+      <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO133" t="inlineStr">
+      <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP133" t="inlineStr">
+      <c r="AP135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR133" t="inlineStr">
+      <c r="AR135" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS133" t="inlineStr"/>
-      <c r="AT133" t="n">
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
         <v>0</v>
       </c>
-      <c r="AU133" t="inlineStr">
+      <c r="AU135" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV133" t="inlineStr">
+      <c r="AV135" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW133" t="inlineStr">
+      <c r="AW135" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
+      <c r="AX135" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY133" t="inlineStr">
+      <c r="AY135" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
+      <c r="AZ135" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA133" t="inlineStr">
+      <c r="BA135" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB133" t="inlineStr">
+      <c r="BB135" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC133" t="inlineStr">
+      <c r="BC135" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -23148,7 +23538,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -23158,7 +23548,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -23178,7 +23568,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -23210,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>568947</v>
+        <v>572190</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7398</v>
+        <v>7404</v>
       </c>
       <c r="O114" t="n">
-        <v>7398</v>
+        <v>7404</v>
       </c>
       <c r="R114" t="n">
-        <v>27.17146184080741</v>
+        <v>27.19349871172452</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21265,13 +21265,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="O123" t="n">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="R123" t="n">
-        <v>19.65584133804872</v>
+        <v>19.67362942975736</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21429,10 +21429,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="O124" t="n">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="O133" t="n">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="R133" t="n">
-        <v>4.358082468617137</v>
+        <v>5.122970412088716</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="O134" t="n">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572190</v>
+        <v>572240</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8114</v>
+        <v>8117</v>
       </c>
       <c r="O95" t="n">
-        <v>8114</v>
+        <v>8117</v>
       </c>
       <c r="R95" t="n">
-        <v>29.80119510358358</v>
+        <v>29.81221353904214</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7404</v>
+        <v>7434</v>
       </c>
       <c r="O114" t="n">
-        <v>7404</v>
+        <v>7434</v>
       </c>
       <c r="R114" t="n">
-        <v>27.19349871172452</v>
+        <v>27.30368306631012</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572240</v>
+        <v>572273</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>288</v>
+        <v>396</v>
       </c>
       <c r="O133" t="n">
-        <v>288</v>
+        <v>396</v>
       </c>
       <c r="R133" t="n">
-        <v>5.122970412088716</v>
+        <v>7.044084316621985</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>288</v>
+        <v>396</v>
       </c>
       <c r="O134" t="n">
-        <v>288</v>
+        <v>396</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572273</v>
+        <v>572381</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -19001,13 +19001,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="O108" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="R108" t="n">
-        <v>21.39043130034058</v>
+        <v>21.39977618076886</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="O109" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572381</v>
+        <v>572382</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="O133" t="n">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="R133" t="n">
-        <v>7.044084316621985</v>
+        <v>8.929622037737969</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="O134" t="n">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572382</v>
+        <v>572488</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8117</v>
+        <v>8119</v>
       </c>
       <c r="O95" t="n">
-        <v>8117</v>
+        <v>8119</v>
       </c>
       <c r="R95" t="n">
-        <v>29.81221353904214</v>
+        <v>29.81955916268117</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7434</v>
+        <v>7488</v>
       </c>
       <c r="O114" t="n">
-        <v>7434</v>
+        <v>7488</v>
       </c>
       <c r="R114" t="n">
-        <v>27.30368306631012</v>
+        <v>27.50201490456419</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -23417,6 +23417,151 @@
         </is>
       </c>
       <c r="BC135" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>14056</v>
+      </c>
+      <c r="O136" t="n">
+        <v>14056</v>
+      </c>
+      <c r="R136" t="n">
+        <v>4.027097599420648</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -23455,7 +23600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -23538,7 +23683,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -23548,7 +23693,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -23600,7 +23745,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>572488</v>
+        <v>586600</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7488</v>
+        <v>7490</v>
       </c>
       <c r="O114" t="n">
-        <v>7488</v>
+        <v>7490</v>
       </c>
       <c r="R114" t="n">
-        <v>27.50201490456419</v>
+        <v>27.50936052820323</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>586600</v>
+        <v>586602</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8119</v>
+        <v>8122</v>
       </c>
       <c r="O95" t="n">
-        <v>8119</v>
+        <v>8122</v>
       </c>
       <c r="R95" t="n">
-        <v>29.81955916268117</v>
+        <v>29.83057759813974</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7490</v>
+        <v>7495</v>
       </c>
       <c r="O114" t="n">
-        <v>7490</v>
+        <v>7495</v>
       </c>
       <c r="R114" t="n">
-        <v>27.50936052820323</v>
+        <v>27.52772458730082</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>502</v>
+        <v>760</v>
       </c>
       <c r="O133" t="n">
-        <v>502</v>
+        <v>760</v>
       </c>
       <c r="R133" t="n">
-        <v>8.929622037737969</v>
+        <v>13.51894969856744</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>502</v>
+        <v>760</v>
       </c>
       <c r="O134" t="n">
-        <v>502</v>
+        <v>760</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23562,6 +23562,151 @@
         </is>
       </c>
       <c r="BC136" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>16885</v>
+      </c>
+      <c r="O137" t="n">
+        <v>16885</v>
+      </c>
+      <c r="R137" t="n">
+        <v>4.837616887181107</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -23600,7 +23745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -23683,7 +23828,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -23693,7 +23838,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -23745,7 +23890,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>586602</v>
+        <v>603753</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>7495</v>
+        <v>7497</v>
       </c>
       <c r="O114" t="n">
-        <v>7495</v>
+        <v>7497</v>
       </c>
       <c r="R114" t="n">
-        <v>27.52772458730082</v>
+        <v>27.53507021093987</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21668,13 +21668,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="O125" t="n">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="R125" t="n">
-        <v>24.14717102668417</v>
+        <v>24.13782614625588</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21832,10 +21832,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="O126" t="n">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -22796,13 +22796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>376</v>
+        <v>7219</v>
       </c>
       <c r="O132" t="n">
-        <v>376</v>
+        <v>7219</v>
       </c>
       <c r="R132" t="n">
-        <v>1.380977244139441</v>
+        <v>26.51402852511337</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>760</v>
+        <v>1026</v>
       </c>
       <c r="O133" t="n">
-        <v>760</v>
+        <v>1026</v>
       </c>
       <c r="R133" t="n">
-        <v>13.51894969856744</v>
+        <v>18.25058209306605</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>760</v>
+        <v>1026</v>
       </c>
       <c r="O134" t="n">
-        <v>760</v>
+        <v>1026</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23709,6 +23709,554 @@
       <c r="BC137" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>13195</v>
+      </c>
+      <c r="O138" t="n">
+        <v>13195</v>
+      </c>
+      <c r="R138" t="n">
+        <v>3.780417816189204</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23745,7 +24293,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -23828,7 +24376,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -23838,7 +24386,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -23858,7 +24406,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -23890,7 +24438,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>603753</v>
+        <v>624058</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -22796,13 +22796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>7219</v>
+        <v>7308</v>
       </c>
       <c r="O132" t="n">
-        <v>7219</v>
+        <v>7308</v>
       </c>
       <c r="R132" t="n">
-        <v>26.51402852511337</v>
+        <v>26.84090877705063</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>624058</v>
+        <v>624147</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -22941,13 +22941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="O133" t="n">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="R133" t="n">
-        <v>18.25058209306605</v>
+        <v>18.94431766970306</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="O134" t="n">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -23924,13 +23924,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>624147</v>
+        <v>624207</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2471,6 +2516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3828,6 +3878,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3976,6 +4031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4124,6 +4184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4272,6 +4337,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4420,6 +4490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4568,6 +4643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4713,6 +4793,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4858,6 +4943,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5003,6 +5093,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5148,6 +5243,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5293,6 +5393,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5438,6 +5543,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5583,6 +5693,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5728,6 +5843,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6263,6 +6383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7620,6 +7745,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7768,6 +7898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7916,6 +8051,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8064,6 +8204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8212,6 +8357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8357,6 +8507,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8502,6 +8657,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8647,6 +8807,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8792,6 +8957,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8937,6 +9107,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9082,6 +9257,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9227,6 +9407,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9372,6 +9557,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9504,10 +9694,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="O56" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -9660,10 +9850,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="O57" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9894,17 +10084,22 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="O58" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="R58" t="n">
-        <v>13.54382058745101</v>
+        <v>13.5660235720206</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -11264,6 +11459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11412,6 +11612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11560,6 +11765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11708,6 +11918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11853,6 +12068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11998,6 +12218,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12143,6 +12368,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12288,6 +12518,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12433,6 +12668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12578,6 +12818,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12723,6 +12968,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12868,6 +13118,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13013,6 +13268,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13145,10 +13405,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="O78" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -13301,10 +13561,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="O79" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -13548,6 +13808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14905,6 +15170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15053,6 +15323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15201,6 +15476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15349,6 +15629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15494,6 +15779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15639,6 +15929,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15784,6 +16079,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15929,6 +16229,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16074,6 +16379,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16219,6 +16529,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16364,6 +16679,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16509,6 +16829,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16654,6 +16979,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16786,10 +17116,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="O100" t="n">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16942,10 +17272,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="O101" t="n">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -17189,6 +17519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18546,6 +18881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18694,6 +19034,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18842,6 +19187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18990,6 +19340,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19135,6 +19490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19280,6 +19640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19425,6 +19790,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19570,6 +19940,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19715,6 +20090,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19860,6 +20240,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20005,6 +20390,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20150,6 +20540,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20295,6 +20690,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20440,6 +20840,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20572,10 +20977,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="O123" t="n">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -20728,10 +21133,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="O124" t="n">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -20923,12 +21328,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20962,24 +21367,19 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>910</v>
+        <v>1172</v>
       </c>
       <c r="O125" t="n">
-        <v>910</v>
+        <v>1172</v>
       </c>
       <c r="R125" t="n">
-        <v>16.18716345486365</v>
+        <v>13.0109489577808</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20987,75 +21387,66 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21473,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -21131,98 +21522,23 @@
       <c r="O126" t="n">
         <v>910</v>
       </c>
+      <c r="R126" t="n">
+        <v>16.18716345486365</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -21321,17 +21637,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21365,22 +21681,39 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>153</v>
+        <v>910</v>
       </c>
       <c r="O127" t="n">
-        <v>153</v>
-      </c>
-      <c r="R127" t="n">
-        <v>38.02857860109512</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>910</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -21388,6 +21721,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21410,11 +21801,11 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
@@ -21423,42 +21814,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21876,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21534,98 +21925,23 @@
       <c r="O128" t="n">
         <v>153</v>
       </c>
+      <c r="R128" t="n">
+        <v>38.02857860109512</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_STI</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Klamydía</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>laboratory_and_registry_diagnoses</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>IS_DOH_sti_current</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -21724,17 +22040,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21768,22 +22084,39 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2086</v>
+        <v>153</v>
       </c>
       <c r="O129" t="n">
-        <v>2086</v>
-      </c>
-      <c r="R129" t="n">
-        <v>19.49342057339906</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>153</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_STI</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Klamydía</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -21791,6 +22124,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>IS_DOH_sti_current</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21803,7 +22194,7 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
@@ -21813,55 +22204,55 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -21888,7 +22279,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -21937,98 +22328,23 @@
       <c r="O130" t="n">
         <v>2086</v>
       </c>
+      <c r="R130" t="n">
+        <v>19.49342057339906</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN130" t="b">
-        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -22127,17 +22443,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22162,7 +22478,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22171,81 +22487,175 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>12263</v>
+        <v>2086</v>
       </c>
       <c r="O131" t="n">
-        <v>12263</v>
-      </c>
-      <c r="R131" t="n">
-        <v>3.513396262215097</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2086</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22307,7 +22717,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22316,17 +22726,22 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>13313</v>
+        <v>12263</v>
       </c>
       <c r="O132" t="n">
-        <v>13313</v>
+        <v>12263</v>
       </c>
       <c r="R132" t="n">
-        <v>3.814225266155883</v>
+        <v>3.513396262215097</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -22452,7 +22867,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22461,17 +22876,22 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>12631</v>
+        <v>13313</v>
       </c>
       <c r="O133" t="n">
-        <v>12631</v>
+        <v>13313</v>
       </c>
       <c r="R133" t="n">
-        <v>3.618829665501011</v>
+        <v>3.814225266155883</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -22597,7 +23017,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -22606,17 +23026,22 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>10277</v>
+        <v>12631</v>
       </c>
       <c r="O134" t="n">
-        <v>10277</v>
+        <v>12631</v>
       </c>
       <c r="R134" t="n">
-        <v>2.944399689047097</v>
+        <v>3.618829665501011</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -22712,12 +23137,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22742,26 +23167,31 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>8122</v>
+        <v>10277</v>
       </c>
       <c r="O135" t="n">
-        <v>8122</v>
+        <v>10277</v>
       </c>
       <c r="R135" t="n">
-        <v>29.83057759813974</v>
+        <v>2.944399689047097</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -22790,42 +23220,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22857,12 +23287,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22896,17 +23326,22 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>75</v>
+        <v>8122</v>
       </c>
       <c r="O136" t="n">
-        <v>75</v>
+        <v>8122</v>
       </c>
       <c r="R136" t="n">
-        <v>15.3165001592916</v>
+        <v>29.83057759813974</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -22940,12 +23375,12 @@
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -22960,12 +23395,12 @@
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
@@ -23002,12 +23437,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23041,17 +23476,22 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>2228</v>
+        <v>75</v>
       </c>
       <c r="O137" t="n">
-        <v>2228</v>
+        <v>75</v>
       </c>
       <c r="R137" t="n">
-        <v>25.69749731981331</v>
+        <v>15.3165001592916</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -23085,7 +23525,7 @@
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
@@ -23105,7 +23545,7 @@
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
@@ -23147,12 +23587,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23186,17 +23626,22 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>211</v>
+        <v>2228</v>
       </c>
       <c r="O138" t="n">
-        <v>211</v>
+        <v>2228</v>
       </c>
       <c r="R138" t="n">
-        <v>78.46812371931469</v>
+        <v>25.69749731981331</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -23230,7 +23675,7 @@
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
@@ -23250,7 +23695,7 @@
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
@@ -23292,12 +23737,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23331,17 +23776,22 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2132</v>
+        <v>211</v>
       </c>
       <c r="O139" t="n">
-        <v>2132</v>
+        <v>211</v>
       </c>
       <c r="R139" t="n">
-        <v>37.14634527527934</v>
+        <v>78.46812371931469</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -23375,7 +23825,7 @@
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
@@ -23395,7 +23845,7 @@
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
@@ -23437,12 +23887,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23476,17 +23926,22 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>467</v>
+        <v>2132</v>
       </c>
       <c r="O140" t="n">
-        <v>467</v>
+        <v>2132</v>
       </c>
       <c r="R140" t="n">
-        <v>24.36306496747765</v>
+        <v>37.14634527527934</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -23520,7 +23975,7 @@
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
@@ -23540,7 +23995,7 @@
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
@@ -23582,12 +24037,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23621,17 +24076,22 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>113</v>
+        <v>467</v>
       </c>
       <c r="O141" t="n">
-        <v>113</v>
+        <v>467</v>
       </c>
       <c r="R141" t="n">
-        <v>19.45957488578263</v>
+        <v>24.36306496747765</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -23665,7 +24125,7 @@
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
@@ -23685,7 +24145,7 @@
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
@@ -23727,12 +24187,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23766,17 +24226,22 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1875</v>
+        <v>113</v>
       </c>
       <c r="O142" t="n">
-        <v>1875</v>
+        <v>113</v>
       </c>
       <c r="R142" t="n">
-        <v>26.20830416057877</v>
+        <v>19.45957488578263</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -23810,7 +24275,7 @@
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
@@ -23830,7 +24295,7 @@
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
@@ -23872,12 +24337,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -23911,17 +24376,22 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1022</v>
+        <v>1875</v>
       </c>
       <c r="O143" t="n">
-        <v>1022</v>
+        <v>1875</v>
       </c>
       <c r="R143" t="n">
-        <v>33.00796906681756</v>
+        <v>26.20830416057877</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -23955,7 +24425,7 @@
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
@@ -23975,7 +24445,7 @@
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
@@ -24017,12 +24487,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24056,19 +24526,17 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>3227</v>
+        <v>1022</v>
       </c>
       <c r="O144" t="n">
-        <v>3227</v>
+        <v>1022</v>
+      </c>
+      <c r="R144" t="n">
+        <v>33.00796906681756</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24078,45 +24546,41 @@
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -24126,17 +24590,17 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
@@ -24168,7 +24632,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24212,103 +24676,25 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>3227</v>
+        <v>3244</v>
       </c>
       <c r="O145" t="n">
-        <v>3227</v>
+        <v>3244</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Chlamydial Infections</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -24402,17 +24788,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24446,22 +24832,39 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>1033</v>
+        <v>3244</v>
       </c>
       <c r="O146" t="n">
-        <v>1033</v>
-      </c>
-      <c r="R146" t="n">
-        <v>18.37509873502654</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3244</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Chlamydial Infections</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -24469,6 +24872,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24476,70 +24937,65 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24566,7 +25022,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -24615,98 +25071,23 @@
       <c r="O147" t="n">
         <v>1033</v>
       </c>
+      <c r="R147" t="n">
+        <v>18.37509873502654</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -24805,17 +25186,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -24849,22 +25230,39 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>2290</v>
+        <v>1033</v>
       </c>
       <c r="O148" t="n">
-        <v>2290</v>
-      </c>
-      <c r="R148" t="n">
-        <v>21.39977618076886</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1033</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -24872,6 +25270,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24884,7 +25340,7 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
@@ -24894,7 +25350,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -24902,47 +25358,47 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24969,7 +25425,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -25018,98 +25474,23 @@
       <c r="O149" t="n">
         <v>2290</v>
       </c>
+      <c r="R149" t="n">
+        <v>21.39977618076886</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -25208,17 +25589,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25243,7 +25624,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25252,81 +25633,175 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>10203</v>
+        <v>2290</v>
       </c>
       <c r="O150" t="n">
-        <v>10203</v>
-      </c>
-      <c r="R150" t="n">
-        <v>2.923198406864604</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2290</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25388,7 +25863,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25397,17 +25872,22 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>13432</v>
+        <v>10203</v>
       </c>
       <c r="O151" t="n">
-        <v>13432</v>
+        <v>10203</v>
       </c>
       <c r="R151" t="n">
-        <v>3.848319219935838</v>
+        <v>2.923198406864604</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -25533,7 +26013,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25542,17 +26022,22 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>13446</v>
+        <v>13432</v>
       </c>
       <c r="O152" t="n">
-        <v>13446</v>
+        <v>13432</v>
       </c>
       <c r="R152" t="n">
-        <v>3.852330273321715</v>
+        <v>3.848319219935838</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -25678,7 +26163,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -25687,17 +26172,22 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>14046</v>
+        <v>13446</v>
       </c>
       <c r="O153" t="n">
-        <v>14046</v>
+        <v>13446</v>
       </c>
       <c r="R153" t="n">
-        <v>4.024232561287879</v>
+        <v>3.852330273321715</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -25793,12 +26283,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -25823,26 +26313,31 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>7497</v>
+        <v>14046</v>
       </c>
       <c r="O154" t="n">
-        <v>7497</v>
+        <v>14046</v>
       </c>
       <c r="R154" t="n">
-        <v>27.53507021093987</v>
+        <v>4.024232561287879</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -25871,42 +26366,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25938,12 +26433,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25977,17 +26472,22 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>83</v>
+        <v>7503</v>
       </c>
       <c r="O155" t="n">
-        <v>83</v>
+        <v>7503</v>
       </c>
       <c r="R155" t="n">
-        <v>16.9502601762827</v>
+        <v>27.55710708185699</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -26021,12 +26521,12 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -26041,12 +26541,12 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
@@ -26083,12 +26583,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26122,17 +26622,22 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2127</v>
+        <v>83</v>
       </c>
       <c r="O156" t="n">
-        <v>2127</v>
+        <v>83</v>
       </c>
       <c r="R156" t="n">
-        <v>24.53257486501029</v>
+        <v>16.9502601762827</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -26166,7 +26671,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -26186,7 +26691,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -26228,12 +26733,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26267,17 +26772,22 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>177</v>
+        <v>2127</v>
       </c>
       <c r="O157" t="n">
-        <v>177</v>
+        <v>2127</v>
       </c>
       <c r="R157" t="n">
-        <v>65.82397108207914</v>
+        <v>24.53257486501029</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -26311,7 +26821,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -26331,7 +26841,7 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -26373,12 +26883,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26412,17 +26922,22 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1897</v>
+        <v>177</v>
       </c>
       <c r="O158" t="n">
-        <v>1897</v>
+        <v>177</v>
       </c>
       <c r="R158" t="n">
-        <v>33.05188414034001</v>
+        <v>65.82397108207914</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -26456,7 +26971,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -26476,7 +26991,7 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
@@ -26518,12 +27033,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26557,17 +27072,22 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>387</v>
+        <v>1897</v>
       </c>
       <c r="O159" t="n">
-        <v>387</v>
+        <v>1897</v>
       </c>
       <c r="R159" t="n">
-        <v>20.18952064756714</v>
+        <v>33.05188414034001</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -26601,7 +27121,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -26621,7 +27141,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -26663,12 +27183,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26702,17 +27222,22 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="O160" t="n">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="R160" t="n">
-        <v>18.94294900385919</v>
+        <v>20.18952064756714</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -26746,7 +27271,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -26766,7 +27291,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -26808,12 +27333,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26847,17 +27372,22 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1667</v>
+        <v>110</v>
       </c>
       <c r="O161" t="n">
-        <v>1667</v>
+        <v>110</v>
       </c>
       <c r="R161" t="n">
-        <v>23.3009296190319</v>
+        <v>18.94294900385919</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -26891,7 +27421,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -26911,7 +27441,7 @@
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
@@ -26953,12 +27483,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26992,17 +27522,22 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1049</v>
+        <v>1667</v>
       </c>
       <c r="O162" t="n">
-        <v>1049</v>
+        <v>1667</v>
       </c>
       <c r="R162" t="n">
-        <v>33.87999956075501</v>
+        <v>23.3009296190319</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -27036,7 +27571,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -27056,7 +27591,7 @@
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
@@ -27098,12 +27633,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27137,22 +27672,17 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="O163" t="n">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="R163" t="n">
-        <v>19.67362942975736</v>
+        <v>33.87999956075501</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -27162,75 +27692,66 @@
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27257,17 +27778,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27301,39 +27822,19 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1106</v>
+        <v>3109</v>
       </c>
       <c r="O164" t="n">
-        <v>1106</v>
+        <v>3109</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -27341,135 +27842,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
         <v>1</v>
       </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT164" t="n">
-        <v>2</v>
-      </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27496,17 +27934,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27540,22 +27978,39 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>2583</v>
+        <v>3109</v>
       </c>
       <c r="O165" t="n">
-        <v>2583</v>
-      </c>
-      <c r="R165" t="n">
-        <v>24.13782614625588</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3109</v>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Chlamydial Infections</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -27563,6 +28018,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27570,7 +28083,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
@@ -27578,62 +28091,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27660,17 +28168,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27704,39 +28212,22 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>2583</v>
+        <v>1106</v>
       </c>
       <c r="O166" t="n">
-        <v>2583</v>
+        <v>1106</v>
+      </c>
+      <c r="R166" t="n">
+        <v>19.67362942975736</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -27744,64 +28235,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
-      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27814,7 +28247,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -27824,7 +28257,7 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT166" t="n">
@@ -27832,47 +28265,47 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27899,17 +28332,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27943,81 +28376,175 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>15153</v>
+        <v>1106</v>
       </c>
       <c r="O167" t="n">
-        <v>15153</v>
-      </c>
-      <c r="R167" t="n">
-        <v>4.341392282585449</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1106</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28049,12 +28576,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28079,7 +28606,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28088,81 +28615,100 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>14684</v>
+        <v>2582</v>
       </c>
       <c r="O168" t="n">
-        <v>14684</v>
+        <v>2582</v>
       </c>
       <c r="R168" t="n">
-        <v>4.207021994158565</v>
+        <v>24.1284812658276</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28189,17 +28735,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28224,7 +28770,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28233,81 +28779,175 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>14554</v>
+        <v>2582</v>
       </c>
       <c r="O169" t="n">
-        <v>14554</v>
-      </c>
-      <c r="R169" t="n">
-        <v>4.169776498432563</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2582</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28369,7 +29009,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28378,17 +29018,22 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>13669</v>
+        <v>15153</v>
       </c>
       <c r="O170" t="n">
-        <v>13669</v>
+        <v>15153</v>
       </c>
       <c r="R170" t="n">
-        <v>3.916220623682472</v>
+        <v>4.341392282585449</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -28514,7 +29159,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28523,17 +29168,22 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>16595</v>
+        <v>14684</v>
       </c>
       <c r="O171" t="n">
-        <v>16595</v>
+        <v>14684</v>
       </c>
       <c r="R171" t="n">
-        <v>4.754530781330795</v>
+        <v>4.207021994158565</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -28629,12 +29279,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -28659,26 +29309,31 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>7396</v>
+        <v>14554</v>
       </c>
       <c r="O172" t="n">
-        <v>7396</v>
+        <v>14554</v>
       </c>
       <c r="R172" t="n">
-        <v>27.16411621716837</v>
+        <v>4.169776498432563</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -28707,42 +29362,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28774,12 +29429,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -28804,26 +29459,31 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>89</v>
+        <v>13669</v>
       </c>
       <c r="O173" t="n">
-        <v>89</v>
+        <v>13669</v>
       </c>
       <c r="R173" t="n">
-        <v>18.17558018902603</v>
+        <v>3.916220623682472</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -28852,42 +29512,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28919,12 +29579,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -28949,26 +29609,31 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2086</v>
+        <v>16595</v>
       </c>
       <c r="O174" t="n">
-        <v>2086</v>
+        <v>16595</v>
       </c>
       <c r="R174" t="n">
-        <v>24.0596855516744</v>
+        <v>4.754530781330795</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -28997,42 +29662,42 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29064,12 +29729,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29103,17 +29768,22 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>80</v>
+        <v>7470</v>
       </c>
       <c r="O175" t="n">
-        <v>80</v>
+        <v>7470</v>
       </c>
       <c r="R175" t="n">
-        <v>29.75094738173069</v>
+        <v>27.43590429181283</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -29147,12 +29817,12 @@
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -29167,12 +29837,12 @@
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
@@ -29209,12 +29879,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29248,17 +29918,22 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1927</v>
+        <v>89</v>
       </c>
       <c r="O176" t="n">
-        <v>1927</v>
+        <v>89</v>
       </c>
       <c r="R176" t="n">
-        <v>33.57458130650247</v>
+        <v>18.17558018902603</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -29292,7 +29967,7 @@
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
@@ -29312,7 +29987,7 @@
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
@@ -29354,12 +30029,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29393,17 +30068,22 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>385</v>
+        <v>2086</v>
       </c>
       <c r="O177" t="n">
-        <v>385</v>
+        <v>2086</v>
       </c>
       <c r="R177" t="n">
-        <v>20.08518203956937</v>
+        <v>24.0596855516744</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -29437,7 +30117,7 @@
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
@@ -29457,7 +30137,7 @@
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
@@ -29499,12 +30179,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29538,17 +30218,22 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="O178" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="R178" t="n">
-        <v>22.04270429539979</v>
+        <v>29.75094738173069</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -29582,7 +30267,7 @@
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
@@ -29602,7 +30287,7 @@
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
@@ -29644,12 +30329,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29683,17 +30368,22 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1604</v>
+        <v>1927</v>
       </c>
       <c r="O179" t="n">
-        <v>1604</v>
+        <v>1927</v>
       </c>
       <c r="R179" t="n">
-        <v>22.42033059923645</v>
+        <v>33.57458130650247</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -29727,7 +30417,7 @@
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
@@ -29747,7 +30437,7 @@
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
@@ -29789,12 +30479,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29828,17 +30518,22 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1009</v>
+        <v>385</v>
       </c>
       <c r="O180" t="n">
-        <v>1009</v>
+        <v>385</v>
       </c>
       <c r="R180" t="n">
-        <v>32.58810253269953</v>
+        <v>20.08518203956937</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -29872,7 +30567,7 @@
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
@@ -29892,7 +30587,7 @@
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
@@ -29934,12 +30629,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -29973,22 +30668,17 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1065</v>
+        <v>128</v>
       </c>
       <c r="O181" t="n">
-        <v>1065</v>
+        <v>128</v>
       </c>
       <c r="R181" t="n">
-        <v>18.94431766970306</v>
+        <v>22.04270429539979</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -29998,75 +30688,66 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30093,17 +30774,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30137,39 +30818,17 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1065</v>
+        <v>1604</v>
       </c>
       <c r="O182" t="n">
-        <v>1065</v>
-      </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1604</v>
+      </c>
+      <c r="R182" t="n">
+        <v>22.42033059923645</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -30177,135 +30836,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN182" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP182" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT182" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV182" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30337,12 +30929,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30367,7 +30959,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -30376,17 +30968,22 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>14539</v>
+        <v>1009</v>
       </c>
       <c r="O183" t="n">
-        <v>14539</v>
+        <v>1009</v>
       </c>
       <c r="R183" t="n">
-        <v>4.16547894123341</v>
+        <v>32.58810253269953</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -30415,42 +31012,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30482,12 +31079,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -30512,7 +31109,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -30521,81 +31118,100 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>14056</v>
+        <v>1083</v>
       </c>
       <c r="O184" t="n">
-        <v>14056</v>
+        <v>1083</v>
       </c>
       <c r="R184" t="n">
-        <v>4.027097599420648</v>
+        <v>19.26450332045861</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30622,17 +31238,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -30657,7 +31273,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -30666,81 +31282,175 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>16885</v>
+        <v>1083</v>
       </c>
       <c r="O185" t="n">
-        <v>16885</v>
-      </c>
-      <c r="R185" t="n">
-        <v>4.837616887181107</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1083</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30772,12 +31482,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -30802,7 +31512,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -30811,81 +31521,100 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>13195</v>
+        <v>2636</v>
       </c>
       <c r="O186" t="n">
-        <v>13195</v>
+        <v>2636</v>
       </c>
       <c r="R186" t="n">
-        <v>3.780417816189204</v>
+        <v>24.6331048089549</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -30912,17 +31641,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -30947,31 +31676,48 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N187" t="n">
-        <v>21</v>
+        <v>2636</v>
       </c>
       <c r="O187" t="n">
-        <v>21</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.3735499258814688</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2636</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -30979,6 +31725,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30991,7 +31795,7 @@
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -31001,7 +31805,7 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -31009,47 +31813,47 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -31076,219 +31880,1133 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>14539</v>
+      </c>
+      <c r="O188" t="n">
+        <v>14539</v>
+      </c>
+      <c r="R188" t="n">
+        <v>4.16547894123341</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>14056</v>
+      </c>
+      <c r="O189" t="n">
+        <v>14056</v>
+      </c>
+      <c r="R189" t="n">
+        <v>4.027097599420648</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>16885</v>
+      </c>
+      <c r="O190" t="n">
+        <v>16885</v>
+      </c>
+      <c r="R190" t="n">
+        <v>4.837616887181107</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>13195</v>
+      </c>
+      <c r="O191" t="n">
+        <v>13195</v>
+      </c>
+      <c r="R191" t="n">
+        <v>3.780417816189204</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
+      <c r="AT191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>194</v>
+      </c>
+      <c r="O192" t="n">
+        <v>194</v>
+      </c>
+      <c r="R192" t="n">
+        <v>3.450889791476427</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>D094</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Chlamydia trachomatis infection</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
         <is>
           <t>沙眼衣原体感染</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="K193" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N188" t="n">
-        <v>21</v>
-      </c>
-      <c r="O188" t="n">
-        <v>21</v>
-      </c>
-      <c r="U188" t="inlineStr">
+      <c r="N193" t="n">
+        <v>194</v>
+      </c>
+      <c r="O193" t="n">
+        <v>194</v>
+      </c>
+      <c r="U193" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
+      <c r="V193" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="W188" t="inlineStr">
+      <c r="W193" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X188" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>Chlamydia</t>
         </is>
       </c>
-      <c r="Y188" t="inlineStr">
+      <c r="Y193" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
+      <c r="Z193" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA188" t="inlineStr">
+      <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
+      <c r="AB193" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC188" t="inlineStr">
+      <c r="AC193" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD188" t="inlineStr">
+      <c r="AD193" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE188" t="inlineStr">
+      <c r="AE193" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF188" t="inlineStr">
+      <c r="AF193" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG188" t="inlineStr">
+      <c r="AG193" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH188" t="inlineStr">
+      <c r="AH193" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI188" t="inlineStr">
+      <c r="AI193" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ188" t="inlineStr">
+      <c r="AJ193" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK188" t="inlineStr">
+      <c r="AK193" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
-      <c r="AM188" t="inlineStr">
+      <c r="AM193" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN188" t="b">
+      <c r="AN193" t="b">
         <v>1</v>
       </c>
-      <c r="AO188" t="inlineStr">
+      <c r="AO193" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP188" t="inlineStr">
+      <c r="AP193" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ188" t="inlineStr">
+      <c r="AQ193" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR188" t="inlineStr">
+      <c r="AR193" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS188" t="inlineStr">
+      <c r="AS193" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="AT188" t="n">
+      <c r="AT193" t="n">
         <v>2</v>
       </c>
-      <c r="AU188" t="inlineStr">
+      <c r="AU193" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV188" t="inlineStr">
+      <c r="AV193" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW188" t="inlineStr">
+      <c r="AW193" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX188" t="inlineStr">
+      <c r="AX193" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY188" t="inlineStr">
+      <c r="AY193" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ188" t="inlineStr">
+      <c r="AZ193" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA188" t="inlineStr">
+      <c r="BA193" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB188" t="inlineStr">
+      <c r="BB193" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC188" t="inlineStr">
+      <c r="BC193" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>16265</v>
+      </c>
+      <c r="O194" t="n">
+        <v>16265</v>
+      </c>
+      <c r="R194" t="n">
+        <v>4.659984522949405</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31325,7 +33043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -31408,7 +33126,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -31418,7 +33136,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -31438,7 +33156,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -31470,7 +33188,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>671344</v>
+        <v>694815</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -26472,13 +26472,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="O155" t="n">
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="R155" t="n">
-        <v>27.55710708185699</v>
+        <v>27.5607798936765</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -29768,13 +29768,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>7470</v>
+        <v>7474</v>
       </c>
       <c r="O175" t="n">
-        <v>7470</v>
+        <v>7474</v>
       </c>
       <c r="R175" t="n">
-        <v>27.43590429181283</v>
+        <v>27.45059553909091</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -32524,13 +32524,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="O192" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="R192" t="n">
-        <v>3.450889791476427</v>
+        <v>4.304718193491213</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -32688,10 +32688,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="O193" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>694815</v>
+        <v>694868</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -21920,13 +21920,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O128" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="R128" t="n">
-        <v>38.02857860109512</v>
+        <v>39.02278980635251</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22084,10 +22084,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O129" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -25430,12 +25430,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25469,13 +25469,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2290</v>
+        <v>179</v>
       </c>
       <c r="O149" t="n">
-        <v>2290</v>
+        <v>179</v>
       </c>
       <c r="R149" t="n">
-        <v>21.39977618076886</v>
+        <v>44.49095143526815</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
@@ -25514,55 +25514,55 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -25594,12 +25594,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25633,29 +25633,29 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2290</v>
+        <v>179</v>
       </c>
       <c r="O150" t="n">
-        <v>2290</v>
+        <v>179</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Klamydía</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -25715,12 +25715,12 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
@@ -25753,55 +25753,55 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -25833,12 +25833,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25863,7 +25863,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25872,86 +25872,100 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>10203</v>
+        <v>2290</v>
       </c>
       <c r="O151" t="n">
-        <v>10203</v>
+        <v>2290</v>
       </c>
       <c r="R151" t="n">
-        <v>2.923198406864604</v>
+        <v>21.39977618076886</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25978,17 +25992,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26013,7 +26027,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26022,86 +26036,175 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>13432</v>
+        <v>2290</v>
       </c>
       <c r="O152" t="n">
-        <v>13432</v>
-      </c>
-      <c r="R152" t="n">
-        <v>3.848319219935838</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2290</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26163,7 +26266,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26172,13 +26275,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="O153" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="R153" t="n">
-        <v>3.852330273321715</v>
+        <v>2.923198406864604</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26313,7 +26416,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26322,13 +26425,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="O154" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="R154" t="n">
-        <v>4.024232561287879</v>
+        <v>3.848319219935838</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26433,12 +26536,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26463,22 +26566,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>7504</v>
+        <v>13446</v>
       </c>
       <c r="O155" t="n">
-        <v>7504</v>
+        <v>13446</v>
       </c>
       <c r="R155" t="n">
-        <v>27.5607798936765</v>
+        <v>3.852330273321715</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26487,7 +26590,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -26516,42 +26619,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26583,12 +26686,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26613,31 +26716,31 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>83</v>
+        <v>14046</v>
       </c>
       <c r="O156" t="n">
-        <v>83</v>
+        <v>14046</v>
       </c>
       <c r="R156" t="n">
-        <v>16.9502601762827</v>
+        <v>4.024232561287879</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -26666,42 +26769,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26733,12 +26836,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26772,17 +26875,17 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>2127</v>
+        <v>7504</v>
       </c>
       <c r="O157" t="n">
-        <v>2127</v>
+        <v>7504</v>
       </c>
       <c r="R157" t="n">
-        <v>24.53257486501029</v>
+        <v>27.5607798936765</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -26821,12 +26924,12 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -26841,12 +26944,12 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
@@ -26883,12 +26986,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26922,13 +27025,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="O158" t="n">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="R158" t="n">
-        <v>65.82397108207914</v>
+        <v>16.9502601762827</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26971,7 +27074,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -26991,7 +27094,7 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
@@ -27033,12 +27136,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27072,13 +27175,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1897</v>
+        <v>2127</v>
       </c>
       <c r="O159" t="n">
-        <v>1897</v>
+        <v>2127</v>
       </c>
       <c r="R159" t="n">
-        <v>33.05188414034001</v>
+        <v>24.53257486501029</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27121,7 +27224,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -27141,7 +27244,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -27183,12 +27286,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27222,13 +27325,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>387</v>
+        <v>177</v>
       </c>
       <c r="O160" t="n">
-        <v>387</v>
+        <v>177</v>
       </c>
       <c r="R160" t="n">
-        <v>20.18952064756714</v>
+        <v>65.82397108207914</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27271,7 +27374,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -27291,7 +27394,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -27333,12 +27436,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27372,13 +27475,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>110</v>
+        <v>1897</v>
       </c>
       <c r="O161" t="n">
-        <v>110</v>
+        <v>1897</v>
       </c>
       <c r="R161" t="n">
-        <v>18.94294900385919</v>
+        <v>33.05188414034001</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27421,7 +27524,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -27441,7 +27544,7 @@
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
@@ -27483,12 +27586,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27522,13 +27625,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1667</v>
+        <v>387</v>
       </c>
       <c r="O162" t="n">
-        <v>1667</v>
+        <v>387</v>
       </c>
       <c r="R162" t="n">
-        <v>23.3009296190319</v>
+        <v>20.18952064756714</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27571,7 +27674,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -27591,7 +27694,7 @@
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
@@ -27633,12 +27736,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27672,13 +27775,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1049</v>
+        <v>110</v>
       </c>
       <c r="O163" t="n">
-        <v>1049</v>
+        <v>110</v>
       </c>
       <c r="R163" t="n">
-        <v>33.87999956075501</v>
+        <v>18.94294900385919</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -27721,7 +27824,7 @@
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
@@ -27741,7 +27844,7 @@
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
@@ -27783,12 +27886,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27822,19 +27925,17 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>3109</v>
+        <v>1667</v>
       </c>
       <c r="O164" t="n">
-        <v>3109</v>
+        <v>1667</v>
+      </c>
+      <c r="R164" t="n">
+        <v>23.3009296190319</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -27844,45 +27945,41 @@
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -27892,17 +27989,17 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
@@ -27934,17 +28031,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27978,39 +28075,17 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>3109</v>
+        <v>1049</v>
       </c>
       <c r="O165" t="n">
-        <v>3109</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Chlamydial Infections</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>1049</v>
+      </c>
+      <c r="R165" t="n">
+        <v>33.87999956075501</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -28018,105 +28093,43 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT165" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV165" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -28126,17 +28139,17 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
@@ -28173,12 +28186,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28212,22 +28225,19 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1106</v>
+        <v>3109</v>
       </c>
       <c r="O166" t="n">
-        <v>1106</v>
-      </c>
-      <c r="R166" t="n">
-        <v>19.67362942975736</v>
+        <v>3109</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -28242,70 +28252,65 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28337,12 +28342,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28376,29 +28381,29 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1106</v>
+        <v>3109</v>
       </c>
       <c r="O167" t="n">
-        <v>1106</v>
+        <v>3109</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>Chlamydia</t>
+          <t>Chlamydial Infections</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -28408,7 +28413,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -28423,7 +28428,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -28458,17 +28463,17 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -28481,70 +28486,65 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28576,12 +28576,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28615,13 +28615,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>2582</v>
+        <v>1106</v>
       </c>
       <c r="O168" t="n">
-        <v>2582</v>
+        <v>1106</v>
       </c>
       <c r="R168" t="n">
-        <v>24.1284812658276</v>
+        <v>19.67362942975736</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -28650,7 +28650,7 @@
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
@@ -28660,7 +28660,7 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT168" t="n">
@@ -28668,47 +28668,47 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28740,12 +28740,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28779,29 +28779,29 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>2582</v>
+        <v>1106</v>
       </c>
       <c r="O169" t="n">
-        <v>2582</v>
+        <v>1106</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Chlamydia</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -28861,17 +28861,17 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -28889,7 +28889,7 @@
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
@@ -28899,7 +28899,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -28907,47 +28907,47 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28979,12 +28979,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -29018,86 +29018,100 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>15153</v>
+        <v>129</v>
       </c>
       <c r="O170" t="n">
-        <v>15153</v>
+        <v>129</v>
       </c>
       <c r="R170" t="n">
-        <v>4.341392282585449</v>
+        <v>32.06331136955079</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -29124,17 +29138,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29159,7 +29173,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29168,86 +29182,175 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>14684</v>
+        <v>129</v>
       </c>
       <c r="O171" t="n">
-        <v>14684</v>
-      </c>
-      <c r="R171" t="n">
-        <v>4.207021994158565</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>129</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_STI</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Klamydía</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>IS_DOH_sti_current</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -29279,12 +29382,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29309,7 +29412,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29318,86 +29421,100 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>14554</v>
+        <v>2582</v>
       </c>
       <c r="O172" t="n">
-        <v>14554</v>
+        <v>2582</v>
       </c>
       <c r="R172" t="n">
-        <v>4.169776498432563</v>
+        <v>24.1284812658276</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29424,17 +29541,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29459,7 +29576,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29468,86 +29585,175 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>13669</v>
+        <v>2582</v>
       </c>
       <c r="O173" t="n">
-        <v>13669</v>
-      </c>
-      <c r="R173" t="n">
-        <v>3.916220623682472</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2582</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29815,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29618,13 +29824,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>16595</v>
+        <v>15153</v>
       </c>
       <c r="O174" t="n">
-        <v>16595</v>
+        <v>15153</v>
       </c>
       <c r="R174" t="n">
-        <v>4.754530781330795</v>
+        <v>4.341392282585449</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29729,12 +29935,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29759,22 +29965,22 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>7474</v>
+        <v>14684</v>
       </c>
       <c r="O175" t="n">
-        <v>7474</v>
+        <v>14684</v>
       </c>
       <c r="R175" t="n">
-        <v>27.45059553909091</v>
+        <v>4.207021994158565</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29783,7 +29989,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -29812,42 +30018,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29879,12 +30085,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29909,31 +30115,31 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>89</v>
+        <v>14554</v>
       </c>
       <c r="O176" t="n">
-        <v>89</v>
+        <v>14554</v>
       </c>
       <c r="R176" t="n">
-        <v>18.17558018902603</v>
+        <v>4.169776498432563</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -29962,42 +30168,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30029,12 +30235,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30059,31 +30265,31 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2086</v>
+        <v>13669</v>
       </c>
       <c r="O177" t="n">
-        <v>2086</v>
+        <v>13669</v>
       </c>
       <c r="R177" t="n">
-        <v>24.0596855516744</v>
+        <v>3.916220623682472</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -30112,42 +30318,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30385,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30209,31 +30415,31 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>80</v>
+        <v>16595</v>
       </c>
       <c r="O178" t="n">
-        <v>80</v>
+        <v>16595</v>
       </c>
       <c r="R178" t="n">
-        <v>29.75094738173069</v>
+        <v>4.754530781330795</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -30262,42 +30468,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30329,12 +30535,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30368,17 +30574,17 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1927</v>
+        <v>7483</v>
       </c>
       <c r="O179" t="n">
-        <v>1927</v>
+        <v>7483</v>
       </c>
       <c r="R179" t="n">
-        <v>33.57458130650247</v>
+        <v>27.48365084546659</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -30417,12 +30623,12 @@
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -30437,12 +30643,12 @@
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
@@ -30479,12 +30685,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30518,13 +30724,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>385</v>
+        <v>89</v>
       </c>
       <c r="O180" t="n">
-        <v>385</v>
+        <v>89</v>
       </c>
       <c r="R180" t="n">
-        <v>20.08518203956937</v>
+        <v>18.17558018902603</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30567,7 +30773,7 @@
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
@@ -30587,7 +30793,7 @@
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
@@ -30629,12 +30835,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30668,13 +30874,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>128</v>
+        <v>2086</v>
       </c>
       <c r="O181" t="n">
-        <v>128</v>
+        <v>2086</v>
       </c>
       <c r="R181" t="n">
-        <v>22.04270429539979</v>
+        <v>24.0596855516744</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -30717,7 +30923,7 @@
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
@@ -30737,7 +30943,7 @@
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
@@ -30779,12 +30985,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30818,13 +31024,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1604</v>
+        <v>80</v>
       </c>
       <c r="O182" t="n">
-        <v>1604</v>
+        <v>80</v>
       </c>
       <c r="R182" t="n">
-        <v>22.42033059923645</v>
+        <v>29.75094738173069</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -30867,7 +31073,7 @@
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
@@ -30887,7 +31093,7 @@
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
@@ -30929,12 +31135,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30968,13 +31174,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1009</v>
+        <v>1927</v>
       </c>
       <c r="O183" t="n">
-        <v>1009</v>
+        <v>1927</v>
       </c>
       <c r="R183" t="n">
-        <v>32.58810253269953</v>
+        <v>33.57458130650247</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -31017,7 +31223,7 @@
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
@@ -31037,7 +31243,7 @@
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
@@ -31079,12 +31285,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -31118,22 +31324,17 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1083</v>
+        <v>385</v>
       </c>
       <c r="O184" t="n">
-        <v>1083</v>
+        <v>385</v>
       </c>
       <c r="R184" t="n">
-        <v>19.26450332045861</v>
+        <v>20.08518203956937</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -31143,75 +31344,66 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31238,17 +31430,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -31282,39 +31474,17 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1083</v>
+        <v>128</v>
       </c>
       <c r="O185" t="n">
-        <v>1083</v>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>128</v>
+      </c>
+      <c r="R185" t="n">
+        <v>22.04270429539979</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -31322,135 +31492,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT185" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV185" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31482,12 +31585,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -31521,22 +31624,17 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>2636</v>
+        <v>1604</v>
       </c>
       <c r="O186" t="n">
-        <v>2636</v>
+        <v>1604</v>
       </c>
       <c r="R186" t="n">
-        <v>24.6331048089549</v>
+        <v>22.42033059923645</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -31546,75 +31644,66 @@
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31641,17 +31730,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -31685,39 +31774,17 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>2636</v>
+        <v>1009</v>
       </c>
       <c r="O187" t="n">
-        <v>2636</v>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1009</v>
+      </c>
+      <c r="R187" t="n">
+        <v>32.58810253269953</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -31725,135 +31792,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="AT187" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV187" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31885,12 +31885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -31924,86 +31924,100 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>14539</v>
+        <v>1083</v>
       </c>
       <c r="O188" t="n">
-        <v>14539</v>
+        <v>1083</v>
       </c>
       <c r="R188" t="n">
-        <v>4.16547894123341</v>
+        <v>19.26450332045861</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32030,17 +32044,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -32065,7 +32079,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -32074,86 +32088,175 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>14056</v>
+        <v>1083</v>
       </c>
       <c r="O189" t="n">
-        <v>14056</v>
-      </c>
-      <c r="R189" t="n">
-        <v>4.027097599420648</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1083</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32185,12 +32288,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -32215,7 +32318,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -32224,86 +32327,100 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>16885</v>
+        <v>146</v>
       </c>
       <c r="O190" t="n">
-        <v>16885</v>
+        <v>146</v>
       </c>
       <c r="R190" t="n">
-        <v>4.837616887181107</v>
+        <v>36.28870899189469</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -32330,17 +32447,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -32365,7 +32482,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -32374,86 +32491,175 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>13195</v>
+        <v>146</v>
       </c>
       <c r="O191" t="n">
-        <v>13195</v>
-      </c>
-      <c r="R191" t="n">
-        <v>3.780417816189204</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>146</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_STI</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Klamydía</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>IS_DOH_sti_current</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -32485,12 +32691,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32515,22 +32721,22 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N192" t="n">
-        <v>242</v>
+        <v>2634</v>
       </c>
       <c r="O192" t="n">
-        <v>242</v>
+        <v>2634</v>
       </c>
       <c r="R192" t="n">
-        <v>4.304718193491213</v>
+        <v>24.61441504809833</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -32539,7 +32745,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -32559,7 +32765,7 @@
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -32569,7 +32775,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -32577,47 +32783,47 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32649,12 +32855,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -32679,38 +32885,38 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N193" t="n">
-        <v>242</v>
+        <v>2634</v>
       </c>
       <c r="O193" t="n">
-        <v>242</v>
+        <v>2634</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>Chlamydia</t>
+          <t>Klamydiainfektion</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -32735,7 +32941,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -32770,17 +32976,17 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -32798,7 +33004,7 @@
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
@@ -32808,7 +33014,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -32816,47 +33022,47 @@
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32918,22 +33124,22 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N194" t="n">
-        <v>16265</v>
+        <v>14539</v>
       </c>
       <c r="O194" t="n">
-        <v>16265</v>
+        <v>14539</v>
       </c>
       <c r="R194" t="n">
-        <v>4.659984522949405</v>
+        <v>4.16547894123341</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -33005,6 +33211,1009 @@
         </is>
       </c>
       <c r="BC194" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>14056</v>
+      </c>
+      <c r="O195" t="n">
+        <v>14056</v>
+      </c>
+      <c r="R195" t="n">
+        <v>4.027097599420648</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
+      <c r="AT195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>16885</v>
+      </c>
+      <c r="O196" t="n">
+        <v>16885</v>
+      </c>
+      <c r="R196" t="n">
+        <v>4.837616887181107</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>13195</v>
+      </c>
+      <c r="O197" t="n">
+        <v>13195</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3.780417816189204</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>314</v>
+      </c>
+      <c r="O198" t="n">
+        <v>314</v>
+      </c>
+      <c r="R198" t="n">
+        <v>5.585460796513392</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>314</v>
+      </c>
+      <c r="O199" t="n">
+        <v>314</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>16265</v>
+      </c>
+      <c r="O200" t="n">
+        <v>16265</v>
+      </c>
+      <c r="R200" t="n">
+        <v>4.659984522949405</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -33126,7 +34335,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -33136,7 +34345,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -33156,7 +34365,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -33188,7 +34397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>694868</v>
+        <v>695405</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -3867,9 +3867,6 @@
       <c r="O20" t="n">
         <v>1199</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.3435180721190493</v>
       </c>
@@ -4015,16 +4012,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10047</v>
+        <v>10045</v>
       </c>
       <c r="O21" t="n">
-        <v>10047</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
+        <v>10045</v>
       </c>
       <c r="R21" t="n">
-        <v>2.878503811993401</v>
+        <v>2.877930804366847</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4168,16 +4162,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>12542</v>
+        <v>12529</v>
       </c>
       <c r="O22" t="n">
-        <v>12542</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
+        <v>12529</v>
       </c>
       <c r="R22" t="n">
-        <v>3.593330826119363</v>
+        <v>3.589606276546763</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4321,16 +4312,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>13995</v>
+        <v>13994</v>
       </c>
       <c r="O23" t="n">
-        <v>13995</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
+        <v>13994</v>
       </c>
       <c r="R23" t="n">
-        <v>4.009620866810755</v>
+        <v>4.009334362997478</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -4479,9 +4467,6 @@
       <c r="O24" t="n">
         <v>11842</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>3.392778156825506</v>
       </c>
@@ -7734,9 +7719,6 @@
       <c r="O43" t="n">
         <v>14148</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>4.053455950242126</v>
       </c>
@@ -7882,16 +7864,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>13689</v>
+        <v>13688</v>
       </c>
       <c r="O44" t="n">
-        <v>13689</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
+        <v>13688</v>
       </c>
       <c r="R44" t="n">
-        <v>3.921950699948012</v>
+        <v>3.921664196134734</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8040,9 +8019,6 @@
       <c r="O45" t="n">
         <v>10049</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>2.879076819619955</v>
       </c>
@@ -8193,9 +8169,6 @@
       <c r="O46" t="n">
         <v>11660</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>3.340634462809103</v>
       </c>
@@ -11040,13 +11013,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="O63" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="R63" t="n">
-        <v>20.45594325751225</v>
+        <v>20.44659837708396</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -11204,10 +11177,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="O64" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -11443,16 +11416,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>13452</v>
+        <v>13440</v>
       </c>
       <c r="O65" t="n">
-        <v>13452</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
+        <v>13440</v>
       </c>
       <c r="R65" t="n">
-        <v>3.854049296201377</v>
+        <v>3.850611250442054</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11596,16 +11566,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>12237</v>
+        <v>12226</v>
       </c>
       <c r="O66" t="n">
-        <v>12237</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
+        <v>12226</v>
       </c>
       <c r="R66" t="n">
-        <v>3.505947163069897</v>
+        <v>3.502795621123851</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -11749,16 +11716,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>13046</v>
+        <v>13032</v>
       </c>
       <c r="O67" t="n">
-        <v>13046</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
+        <v>13032</v>
       </c>
       <c r="R67" t="n">
-        <v>3.73772874801094</v>
+        <v>3.733717694625063</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -11902,16 +11866,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>12157</v>
+        <v>12137</v>
       </c>
       <c r="O68" t="n">
-        <v>12157</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
+        <v>12137</v>
       </c>
       <c r="R68" t="n">
-        <v>3.483026858007742</v>
+        <v>3.477296781742203</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -15154,16 +15115,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>10830</v>
+        <v>10822</v>
       </c>
       <c r="O87" t="n">
-        <v>10830</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
+        <v>10822</v>
       </c>
       <c r="R87" t="n">
-        <v>3.102836297789244</v>
+        <v>3.100544267283029</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15307,16 +15265,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>10703</v>
+        <v>10693</v>
       </c>
       <c r="O88" t="n">
-        <v>10703</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
+        <v>10693</v>
       </c>
       <c r="R88" t="n">
-        <v>3.066450313503073</v>
+        <v>3.063585275370304</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -15460,16 +15415,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>13375</v>
+        <v>13367</v>
       </c>
       <c r="O89" t="n">
-        <v>13375</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
+        <v>13367</v>
       </c>
       <c r="R89" t="n">
-        <v>3.831988502579053</v>
+        <v>3.829696472072837</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15613,16 +15565,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>14475</v>
+        <v>14467</v>
       </c>
       <c r="O90" t="n">
-        <v>14475</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
+        <v>14467</v>
       </c>
       <c r="R90" t="n">
-        <v>4.147142697183685</v>
+        <v>4.14485066667747</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18462,13 +18411,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="O107" t="n">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="R107" t="n">
-        <v>19.09159071498287</v>
+        <v>19.05421119326974</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -18626,10 +18575,10 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="O108" t="n">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -18865,16 +18814,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>13174</v>
+        <v>13159</v>
       </c>
       <c r="O109" t="n">
-        <v>13174</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
+        <v>13159</v>
       </c>
       <c r="R109" t="n">
-        <v>3.774401236110388</v>
+        <v>3.770103678911234</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19018,16 +18964,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>9872</v>
+        <v>9854</v>
       </c>
       <c r="O110" t="n">
-        <v>9872</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
+        <v>9854</v>
       </c>
       <c r="R110" t="n">
-        <v>2.828365644669937</v>
+        <v>2.823208576030952</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19171,16 +19114,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>13193</v>
+        <v>13179</v>
       </c>
       <c r="O111" t="n">
-        <v>13193</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
+        <v>13179</v>
       </c>
       <c r="R111" t="n">
-        <v>3.77984480856265</v>
+        <v>3.775833755176773</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -19324,16 +19264,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>3506</v>
+        <v>3486</v>
       </c>
       <c r="O112" t="n">
-        <v>3506</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
+        <v>3486</v>
       </c>
       <c r="R112" t="n">
-        <v>1.004482369348946</v>
+        <v>0.9987522930834078</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -25872,13 +25809,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="O151" t="n">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="R151" t="n">
-        <v>21.39977618076886</v>
+        <v>21.37174153948401</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -26036,10 +25973,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="O152" t="n">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -34214,6 +34151,156 @@
         </is>
       </c>
       <c r="BC200" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>13603</v>
+      </c>
+      <c r="O201" t="n">
+        <v>13603</v>
+      </c>
+      <c r="R201" t="n">
+        <v>3.897311372006194</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34252,7 +34339,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -34335,7 +34422,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -34345,7 +34432,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -34397,7 +34484,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>695405</v>
+        <v>708825</v>
       </c>
     </row>
     <row r="16">
